--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
@@ -360,55 +360,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C1" s="0">
+      <x:c r="C1">
         <x:v>-20</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>-60</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A1:A4">
     <x:cfRule type="dataBar" priority="1">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="min" val="0"/>
         <x:cfvo type="max" val="0"/>
         <x:color rgb="FF008000"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba51641a-8cad-4020-ac9f-9887ac308304}</x14:id>
+          <x14:id>{51e33ba8-75c2-4668-b76e-e2a373311dac}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -422,22 +419,18 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4f0765a-4f73-4119-8291-090caa213f96}</x14:id>
+          <x14:id>{3721b92f-283a-4292-b0aa-315d9f9e0f0d}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba51641a-8cad-4020-ac9f-9887ac308304}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{51e33ba8-75c2-4668-b76e-e2a373311dac}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
               </x14:cfvo>
@@ -451,8 +444,8 @@
           <xm:sqref>A1:A4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4f0765a-4f73-4119-8291-090caa213f96}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="0" gradient="1">
+          <x14:cfRule type="dataBar" id="{3721b92f-283a-4292-b0aa-315d9f9e0f0d}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="0">
               <x14:cfvo type="num">
                 <xm:f>-100</xm:f>
               </x14:cfvo>
